--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N103_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N103_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>64.50790932302127</v>
+        <v>10.48253526499096</v>
       </c>
       <c r="D2" t="n">
-        <v>30.00416637735499</v>
+        <v>4.875677036320186</v>
       </c>
       <c r="E2" t="n">
-        <v>17.94856926697226</v>
+        <v>2.916642505882993</v>
       </c>
       <c r="F2" t="n">
-        <v>9.091997475223719</v>
+        <v>1.477449589723854</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.72930792016958</v>
+        <v>7.756012537027558</v>
       </c>
       <c r="D3" t="n">
-        <v>41.86287137786896</v>
+        <v>6.802716598903706</v>
       </c>
       <c r="E3" t="n">
-        <v>17.94856926697226</v>
+        <v>2.916642505882993</v>
       </c>
       <c r="F3" t="n">
-        <v>9.091997475223719</v>
+        <v>1.477449589723854</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.930600743202156</v>
+        <v>1.61372262077035</v>
       </c>
       <c r="D4" t="n">
-        <v>18.91340663276876</v>
+        <v>3.073428577824923</v>
       </c>
       <c r="E4" t="n">
-        <v>17.94856926697226</v>
+        <v>2.916642505882993</v>
       </c>
       <c r="F4" t="n">
-        <v>9.091997475223719</v>
+        <v>1.477449589723854</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>38.75767796996531</v>
+        <v>6.298122670119364</v>
       </c>
       <c r="D5" t="n">
-        <v>17.21421863042876</v>
+        <v>2.797310527444673</v>
       </c>
       <c r="E5" t="n">
-        <v>17.94856926697226</v>
+        <v>2.916642505882993</v>
       </c>
       <c r="F5" t="n">
-        <v>9.091997475223719</v>
+        <v>1.477449589723854</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>47.72118985352861</v>
+        <v>7.7546933511984</v>
       </c>
       <c r="D6" t="n">
-        <v>32.27095499296201</v>
+        <v>5.244030186356327</v>
       </c>
       <c r="E6" t="n">
-        <v>17.94856926697226</v>
+        <v>2.916642505882993</v>
       </c>
       <c r="F6" t="n">
-        <v>9.091997475223719</v>
+        <v>1.477449589723854</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
